--- a/weekly_temp/patents_低温环境系统.xlsx
+++ b/weekly_temp/patents_低温环境系统.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,222 +456,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>用于在低温工作温度下操作一组量子比特的系统和方法</t>
+          <t>接收方小型化量子密钥生成终端</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>荷兰应用自然科学研究组织</t>
+          <t>科大国盾量子技术股份有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VAN ZWET, ERWIN JOHN</t>
+          <t>杜先常 | 唐世彪 | 陈国靖 | 董军</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本发明提供了一种用于在低温工作温度 (Tq) 下操作一组量子位 (10q) 的系统 (100) 和方法。该系统包括第一基板 (10) 和第二基板 (20),它们通过一组连接器 (30) 电连接。第一基板 (10) 包含一组量子位 (10q),第二基板 (20) 包含配置用于操作该组量子位 (10q) 的电子器件 (21)。第一冷却元件 (41) 将第一基板 (10) 保持在低于低温工作温度 (Tq) 的第一低温温度 (T1),第二冷却元件 (42) 将第二基板 (20) 保持在高于低温工作温度 (Tq) 的第二低温温度 (T2)。该组连接器(30)被配置为将第二基板(20)和第一基板(10)之间的热流保持在足够低的阈值以下,以将一组量子位(10q)维持在低温工作温度(Tq)。</t>
+          <t>本发明提供一种接收方小型化量子密钥生成终端，包括机箱(1)、主控板(2)、探测器模块(3)、解码光路(4)、电源(5)和风扇(6)，主控板(2)和解码光路(4)左右并排设置，并且主控板(2)和解码光路(4)的前端抵在机箱(1)的前面板的内部，探测器模块(3)与解码光路(4)前后并排设置，且探测器模块(3)与解码光路(4)的左端部均紧挨主控板(2)的右端部；电源(5)设置在机箱(1)的后部，吹风风扇(6)设置在靠近探测器模块(3)的一侧。本发明的优点在于：在保证通信可靠性的前提下实现了接收方量子密钥生成终端的小型化，经热仿真和力仿真测试，热设计和力设计满足设备使用要求。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=8f619a02-cea9-462f-9e6e-4dca613a46ae&amp;shareId=E41F3B0F-9352-71B8-3F94-09F7G7CDE08G&amp;from=EXPORT&amp;signature=AHBRRSlZDoMjNQwrWLsszX7nPvGbNQFEffsWap38SDI%3D&amp;expire=94608000&amp;date=20260529T004228Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f4921438-27c2-41b2-a5af-afb2aa2b757f&amp;shareId=9822D43G-CCG6-9909-3EB1-2F5994384B2D&amp;from=EXPORT&amp;signature=IekkCgLKSsSp53YhWWg8X8KWGbrIraDcr9lDYUnXcIY%3D&amp;expire=94608000&amp;date=20260605T003852Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>一种基于热电转换效应的笔记本电脑废热回收利用系统及方法</t>
+          <t>采用量子处理单元(QPU)的图形处理单元(GPU)叠加计算系统</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>百信信息技术有限公司 | 安徽百信信息技术有限公司</t>
+          <t>芯科量子公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>王宪朝 | 鞠荣荣 | 汪玲 | 陶方强 | 黄巧林 | 曾盛坚 | 胡晓雨</t>
+          <t>ハッチングス, マシュー | ムカノフ, オレグ | レヴィ, ジョン</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本发明公开了一种基于热电转换效应的笔记本电脑废热回收利用系统及方法，涉及热电材料与器件技术领域，包括：分布式热电阵列模块：由多个微型TEG单元组成，分布于笔记本高发热区域，通过温差直接发电；自适应热管理模块：包括导热硅胶层与微型散热鳍片，优化热端与冷端的温差；多级电能管理模块：包括整流电路、DC‑DC升压芯片及回收储能电池装置，将TEG输出的不稳定低压直流电转换为稳定电能，储存后供给目标设备；智能控制模块：根据温度传感器数据动态调整微型热电发电单元的工作区域，优先选择温差最大的位置发电，并通过PMIC芯片匹配供电需求。本发明通过创新设计实现废热高效转换及利用，解决小型化设备中热电转换效率低的问题，实现节能与环保。</t>
+          <t>本专利文件提供了一种高效的量子-经典混合计算系统的设计方案,该系统能够基于量子计算(利用量子比特的不同量子态)和经典数字计算(利用包含一个或多个图形处理单元(GPU)处理器的数字处理器)进行信息处理。本发明提供了一种采用量子处理单元(QPU)的图形处理单元(GPU)叠加计算系统。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=79c9d744-08d0-473f-a097-08a12218cd8d&amp;shareId=E41F3B0F-9352-71B8-3F94-09F7G7CDE08G&amp;from=EXPORT&amp;signature=SQaExLyYD5Q3%2BfTRTRBNRh3wn8E6JLI36uURJgZpuYc%3D&amp;expire=94608000&amp;date=20260529T004228Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>温度梯度控制的蒸发造粒塔制备煤基量子碳点缓释肥料的方法</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>北京天中树科技发展有限公司</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>吴则昀 | 吴则一 | 朱光华</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>本发明提供了温度梯度控制的蒸发造粒塔制备煤基量子碳点缓释肥料的方法，涉及农业肥料制备技术领域，包括在蒸发造粒塔内部自下至上设置高温区、中温区和低温区、煤粉与超临界水混合在高温区反应生成量子碳点前驱体、量子碳点前驱体在中温区内部通过氨气吹扫后与硼酸溶液反应、碳点溶液与尿素熔融液混合、双混液在低温区通过双流体喷嘴雾化形成复合肥料颗粒、在流化床包衣机内喷入氧化海藻酸钠/聚乙二醇复合膜溶液对复合肥料颗粒进行包衣；本发明在蒸发造粒塔内部自下至上设置高温区、中温区和低温区，实现将量子碳点合成、表面修饰、肥料复合三大核心工序集成于同一设备内，避免了跨设备操作导致的量子碳点结构破坏，保证产物稳定性。</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=2bee4aa4-7314-4d65-bd8f-580b34cdbd8a&amp;shareId=E41F3B0F-9352-71B8-3F94-09F7G7CDE08G&amp;from=EXPORT&amp;signature=u2YngjdHVkBZdvCJNaUqLtPNSreVyoIsxHyVwGhVzaY%3D&amp;expire=94608000&amp;date=20260529T004228Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>一种高浓度尿素废水中非挥发性酸根定向去除与尿素回收的方法和系统</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>宜兴鸿微环保科技有限公司</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>李侃 | 高启新 | 华佳 | 安丽娟</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>本发明公开了一种高浓度尿素废水中非挥发性酸根定向去除与尿素回收的方法和系统，属于废水处理与资源回收技术领域。该方法先将废水引入预处理单元，投加碱金属盐、有机络合剂与纳米催化颗粒复配而成的协同处理剂，定向沉淀非挥发性酸根形成致密沉淀物；再通过超声辅助卧式螺旋卸料沉降离心机完成强化固液分离，上清液经石墨烯量子点‑温度响应性磁性纳米粒子复合改性阴离子交换树脂深度吸附残留酸根，实现酸根近乎完全去除；随后采用低温蒸发‑余热回收耦合工艺浓缩尿素，经分段温度‑压力梯度结晶析出高纯度尿素晶体；吸附饱和的树脂通过磁场分离回收，经温度调控温和再生后循环复用；适用于工业高浓度尿素废水资源化处理。</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=9d646539-046f-4512-a61b-935b36551599&amp;shareId=E41F3B0F-9352-71B8-3F94-09F7G7CDE08G&amp;from=EXPORT&amp;signature=jhY6zmTgOZsn%2BHBeS26e7YxBuQimizNLsLFV7Jpn604%3D&amp;expire=94608000&amp;date=20260529T004228Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>一种高性能深紫外发光器件及其制备方法</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>北京大学</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>王新强 | 李泰 | 刘放 | 马文结 | 袁泽兴 | 刘一欣 | 王超雨 | 王平</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>本发明公开了一种高性能深紫外发光器件及其制备方法，属于半导体外延生长技术领域。本发明通过构建预制压应力结合受限减薄的协同机制，制备超薄量子阱并引入有效的压应力，以实现能带调控提升量子阱的TE偏振发光占比，解决了现有深紫外发光器件中量子阱应力引入与结构稳定性难以兼顾的技术难题。第二超晶格层使随后外延的量子阱在生长过程中受到受控的外部压应力；通过受控减薄形成的超薄量子阱具有增强的量子限制效应，与预置压应力协同作用，使价带顶态的能量排序向有利于TE跃迁的方向移动，从而有效抑制TM分量并显著提升TE发光占比。本发明为深紫外发光器件在紫外消毒、医疗、环境监测及精密光学等领域的应用提供了可行的制备基础。</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=26d84603-c7ad-444d-b34d-4e57623f1ad3&amp;shareId=E41F3B0F-9352-71B8-3F94-09F7G7CDE08G&amp;from=EXPORT&amp;signature=qYosjKe3ZQri2d4ISd9KCR0rTig2acL9jIeLeLwqaCw%3D&amp;expire=94608000&amp;date=20260529T004228Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>用于量子计算测控的集成滤波放大装置</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>相干(北京)科技有限公司</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>赵剑琴 | 邢磊 | 田建强 | 贺玉龙 | 曾祥洪</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>本申请涉及一种用于量子计算测控的集成滤波放大装置，包括：装置壳体、电路板、前端衰减组件、前端带通滤波组件、微波放大组件、后端衰减组件和后端带通滤波组件，前端带通滤波组件、前端衰减组件、微波放大组件、后端衰减组件和后端带通滤波组件，依次连接设置在所述电路板上，且均集成在装置壳体内，通过集成带通滤波器、衰减器和微波放大器的微波前端模块，极大降低了外部线路复杂性，且该集成前端模块体积小，可直接集成到电子学设备中，使得测控脉冲从电子学设备中发生后可直接接入稀释制冷机内，极大简化了外部接线，提升了系统可靠性。</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=02fd591a-9387-4d8e-abef-42688565ec39&amp;shareId=E41F3B0F-9352-71B8-3F94-09F7G7CDE08G&amp;from=EXPORT&amp;signature=1JKZo99fgnMuYC9TeyIO%2BH%2BfMQnWDXkJ55m91pPdA8A%3D&amp;expire=94608000&amp;date=20260529T004228Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=790c2d97-855b-4e0a-9871-d310eb385917&amp;shareId=9822D43G-CCG6-9909-3EB1-2F5994384B2D&amp;from=EXPORT&amp;signature=hpf9T4zP2CQGVclG38u8YABrx6n70ujlX9k7YrglEcI%3D&amp;expire=94608000&amp;date=20260605T003852Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_低温环境系统.xlsx
+++ b/weekly_temp/patents_低温环境系统.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>接收方小型化量子密钥生成终端</t>
+          <t>一种多端口频分复用滤波器</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科大国盾量子技术股份有限公司</t>
+          <t>清华大学 | 无锡东微量子科技有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杜先常 | 唐世彪 | 陈国靖 | 董军</t>
+          <t>戴根婷 | 杨亮亮 | 何楷泳 | 耿霄 | 程明俊 | 陈国动 | 孟范忠 | 陈宏江 | 刘建设 | 陈炜</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,54 +476,128 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本发明提供一种接收方小型化量子密钥生成终端，包括机箱(1)、主控板(2)、探测器模块(3)、解码光路(4)、电源(5)和风扇(6)，主控板(2)和解码光路(4)左右并排设置，并且主控板(2)和解码光路(4)的前端抵在机箱(1)的前面板的内部，探测器模块(3)与解码光路(4)前后并排设置，且探测器模块(3)与解码光路(4)的左端部均紧挨主控板(2)的右端部；电源(5)设置在机箱(1)的后部，吹风风扇(6)设置在靠近探测器模块(3)的一侧。本发明的优点在于：在保证通信可靠性的前提下实现了接收方量子密钥生成终端的小型化，经热仿真和力仿真测试，热设计和力设计满足设备使用要求。</t>
+          <t>本申请公开了一种多端口频分复用滤波器，包括：一个或一个以上选频滤波模块，每个所述选频滤波模块设置一个输入端口，一个或一个以上输出端口；每个所述选频滤波模块包括：一个或一个以上耦合模块、一个或一个以上不同频率的谐振腔；耦合模块，用于将经由输入端口输入的一段频率信号耦合到不同频率的谐振腔；谐振腔，用于完成对应频率信号的选择性传递，并从对应的输出端口输出。通过本申请实施例实现了可调频段的单腔体带通滤波功能。不仅能解决超导量子计算领域中XY控制线端口复用的问题，而且具备在其他应用领域实现多段式频分复用功能的潜力，突破对于推动量子处理器的规模化扩展具有重大意义。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f4921438-27c2-41b2-a5af-afb2aa2b757f&amp;shareId=9822D43G-CCG6-9909-3EB1-2F5994384B2D&amp;from=EXPORT&amp;signature=IekkCgLKSsSp53YhWWg8X8KWGbrIraDcr9lDYUnXcIY%3D&amp;expire=94608000&amp;date=20260605T003852Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=843949ff-4186-4691-b320-a19f523d5d73&amp;shareId=193FC1D0-D471-7F90-B17C-E5CE67738GC2&amp;from=EXPORT&amp;signature=aJUzGZXrbtcmlPQp886n88Uh40i65wr%2FbHJRscldW9s%3D&amp;expire=94608000&amp;date=20260626T004136Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>采用量子处理单元(QPU)的图形处理单元(GPU)叠加计算系统</t>
+          <t>集成式量子比特输出链路</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>芯科量子公司</t>
+          <t>相干(北京)科技有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ハッチングス, マシュー | ムカノフ, オレグ | レヴィ, ジョン</t>
+          <t>赵剑琴</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本专利文件提供了一种高效的量子-经典混合计算系统的设计方案,该系统能够基于量子计算(利用量子比特的不同量子态)和经典数字计算(利用包含一个或多个图形处理单元(GPU)处理器的数字处理器)进行信息处理。本发明提供了一种采用量子处理单元(QPU)的图形处理单元(GPU)叠加计算系统。</t>
+          <t>本申请提出了一种集成式量子比特输出链路，涉及输入/输出装置的链路技术领域。本申请所要解决的问题是，量子比特传输时，空间受限，难以实现高效的热处理。本申请提出的集成式量子比特输出链路，包括：三节环形器；负载，负载设置在三节环形器上，负载用于吸收反向传输的信号；约瑟夫森参量放大器，约瑟夫森参量放大器内置有连接器，约瑟夫森参量放大器通过连接器连接三节环形器。本实用新型提出的集成式量子比特输出链路，使得量子比特可以在超级低温环境下依然保持良好的性能，达到了高集成、高导热和磁屏蔽的效果，并且易于装配和大批量生产，有效减小集成式量子比特输出链路的体积。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=790c2d97-855b-4e0a-9871-d310eb385917&amp;shareId=9822D43G-CCG6-9909-3EB1-2F5994384B2D&amp;from=EXPORT&amp;signature=hpf9T4zP2CQGVclG38u8YABrx6n70ujlX9k7YrglEcI%3D&amp;expire=94608000&amp;date=20260605T003852Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=71a205ba-d0c8-4143-9495-276d9dffd4d6&amp;shareId=193FC1D0-D471-7F90-B17C-E5CE67738GC2&amp;from=EXPORT&amp;signature=8rAQrUaJLOyh3l%2FNaVcvS71ZGhvTwJzCRWQdo0zECAw%3D&amp;expire=94608000&amp;date=20260626T004136Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>利用石墨烯的基于卡西米尔效应的隧道晶体管</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>QUBIT SEMICONDUCTOR LLC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DANNEMILLER, DOUGLAS JOSEPH</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>一种量子器件包括:致动器,其包含石墨烯材料,且近端安装于致动器锚点;电极,其位于致动器的远端;量子点,其配置用于局域单个电子,该量子点和电极位于同一真空中以形成隧穿间隙;以及量子点锚点,其包含石墨烯材料,相对于电极与量子点位于同一平面。该量子器件可包括调制器,其配置用于发射特定频率范围内的电磁信号。石墨烯材料被调谐以响应电磁信号而增强电极和量子点锚点之间的卡西米尔力。增强的卡西米尔力使致动器发生形变,从而使电极进入量子点的电子隧穿范围,或者降低静态电极上的隧穿势垒。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=78e78df7-d44b-4d39-9591-c546be0473f8&amp;shareId=193FC1D0-D471-7F90-B17C-E5CE67738GC2&amp;from=EXPORT&amp;signature=kEqkH37DeThYozUBJyinFYrTEiUZpx1LUXH3yFZeneU%3D&amp;expire=94608000&amp;date=20260626T004136Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>包含量子电容器的参数放大器</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>微软技术许可有限责任公司</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>萊利 大衛J</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>描述了与包括量子电容器的参数放大器有关的系统及方法。在一个实例中,提供了包含用于接收量子位元信号的输入端子的参数放大器。参数放大器进一步包括用于接收泵送信号的泵送端子。参数放大器进一步包含放大器,该放大器包括复数个量子电容装置,该复数个量子电容装置经配置以在低温环境中操作,并经配置以借由将量子位元信号与泵送信号混合以产生放大信号来放大量子位元信号。参数放大器进一步包括用于提供放大信号的输出端子。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=a933b1a4-1ee7-4584-8654-0684310adaba&amp;shareId=193FC1D0-D471-7F90-B17C-E5CE67738GC2&amp;from=EXPORT&amp;signature=6jWGghLF01f49p61BaiFOq9zGIxcB5bNew4wkAPdLaI%3D&amp;expire=94608000&amp;date=20260626T004136Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_低温环境系统.xlsx
+++ b/weekly_temp/patents_低温环境系统.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>一种多端口频分复用滤波器</t>
+          <t>一种离子阱及量子计算装置</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>清华大学 | 无锡东微量子科技有限公司</t>
+          <t>华翊博奥(北京)量子科技有限公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>戴根婷 | 杨亮亮 | 何楷泳 | 耿霄 | 程明俊 | 陈国动 | 孟范忠 | 陈宏江 | 刘建设 | 陈炜</t>
+          <t>毛志超 | 蔡明磊 | 梅全鑫 | 赵文定</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,108 +476,108 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本申请公开了一种多端口频分复用滤波器，包括：一个或一个以上选频滤波模块，每个所述选频滤波模块设置一个输入端口，一个或一个以上输出端口；每个所述选频滤波模块包括：一个或一个以上耦合模块、一个或一个以上不同频率的谐振腔；耦合模块，用于将经由输入端口输入的一段频率信号耦合到不同频率的谐振腔；谐振腔，用于完成对应频率信号的选择性传递，并从对应的输出端口输出。通过本申请实施例实现了可调频段的单腔体带通滤波功能。不仅能解决超导量子计算领域中XY控制线端口复用的问题，而且具备在其他应用领域实现多段式频分复用功能的潜力，突破对于推动量子处理器的规模化扩展具有重大意义。</t>
+          <t>本文公开一种离子阱及量子计算装置，包括：一体化基片，制备于一体化基片上的射频电极和直流电极；其中，一体化基片具有轴向的通光开槽。本发明实施例离子阱基于一体化基片设计，消除了温度变化带来的分体错位问题，使得离子阱可以应用于低温环境；通过开放的开槽使离子阱获得了开放式的轴向通光，具有更高的数值孔径，增加了离子阱通光自由度，为实现量子计算的大规模应用提供支持。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=843949ff-4186-4691-b320-a19f523d5d73&amp;shareId=193FC1D0-D471-7F90-B17C-E5CE67738GC2&amp;from=EXPORT&amp;signature=aJUzGZXrbtcmlPQp886n88Uh40i65wr%2FbHJRscldW9s%3D&amp;expire=94608000&amp;date=20260626T004136Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=812af80b-4741-463b-ab78-d83bde6bb6e8&amp;shareId=52BD9CD7-45FG-8274-0137-9D20G0FC1569&amp;from=EXPORT&amp;signature=5LLF1Ckm3n6GVgymHmMHuQotzmM%2BQT%2Bnh9DyXO%2FReCA%3D&amp;expire=94608000&amp;date=20260710T002807Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>集成式量子比特输出链路</t>
+          <t>一种兼具耐电晕与导热性能的复合纳米芳纶绝缘纸及其制备与应用</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>相干(北京)科技有限公司</t>
+          <t>四川大学</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>赵剑琴</t>
+          <t>任俊文 | 张稼珵 | 王梓 | 高萌 | 谭淋 | 陈俊雪 | 龙志慧</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本申请提出了一种集成式量子比特输出链路，涉及输入/输出装置的链路技术领域。本申请所要解决的问题是，量子比特传输时，空间受限，难以实现高效的热处理。本申请提出的集成式量子比特输出链路，包括：三节环形器；负载，负载设置在三节环形器上，负载用于吸收反向传输的信号；约瑟夫森参量放大器，约瑟夫森参量放大器内置有连接器，约瑟夫森参量放大器通过连接器连接三节环形器。本实用新型提出的集成式量子比特输出链路，使得量子比特可以在超级低温环境下依然保持良好的性能，达到了高集成、高导热和磁屏蔽的效果，并且易于装配和大批量生产，有效减小集成式量子比特输出链路的体积。</t>
+          <t>本发明公开了一种兼具耐电晕与导热性能的复合纳米芳纶绝缘纸及其制备与应用，绝缘纸由芳纶纳米纤维基体以及均匀分散于芳纶纳米纤维基体中的第一功能填料和第二功能填料组成；第一功能填料为经表面功能化处理的氮化硼量子点；第二功能填料为纳米碳化硅；经表面功能化处理的氮化硼量子点的质量为芳纶纳米纤维基体质量的1%~15%，纳米碳化硅质量为芳纶纳米纤维基体质量的0.5%~8%。经表面功能化处理的氮化硼量子点的平均粒径为2nm~10 nm。本发明解决了现有技术缺乏紫外防护机制，填料分布不可控，工艺复杂导热有限的问题，通过电场调控、紫外防护和复合填料优化分布的协同作用，显著提升绝缘纸的耐电晕性能和导热性能。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=71a205ba-d0c8-4143-9495-276d9dffd4d6&amp;shareId=193FC1D0-D471-7F90-B17C-E5CE67738GC2&amp;from=EXPORT&amp;signature=8rAQrUaJLOyh3l%2FNaVcvS71ZGhvTwJzCRWQdo0zECAw%3D&amp;expire=94608000&amp;date=20260626T004136Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=3c0b5980-c120-43ac-958a-9b3227662b88&amp;shareId=52BD9CD7-45FG-8274-0137-9D20G0FC1569&amp;from=EXPORT&amp;signature=FycS9fUCKgWV4S3%2Fz0DP0GPwtafHKS%2ByrL9SPMvngXs%3D&amp;expire=94608000&amp;date=20260710T002807Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>利用石墨烯的基于卡西米尔效应的隧道晶体管</t>
+          <t>一种量子点与电磁感应协同配合的电池热管理装置</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QUBIT SEMICONDUCTOR LLC</t>
+          <t>安徽理工大学</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DANNEMILLER, DOUGLAS JOSEPH</t>
+          <t>盛国超 | 朱浩冉 | 张妮 | 冯林涛 | 陈晖</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>一种量子器件包括:致动器,其包含石墨烯材料,且近端安装于致动器锚点;电极,其位于致动器的远端;量子点,其配置用于局域单个电子,该量子点和电极位于同一真空中以形成隧穿间隙;以及量子点锚点,其包含石墨烯材料,相对于电极与量子点位于同一平面。该量子器件可包括调制器,其配置用于发射特定频率范围内的电磁信号。石墨烯材料被调谐以响应电磁信号而增强电极和量子点锚点之间的卡西米尔力。增强的卡西米尔力使致动器发生形变,从而使电极进入量子点的电子隧穿范围,或者降低静态电极上的隧穿势垒。</t>
+          <t>本发明提供一种量子点与电磁感应协同配合的电池热管理装置，涉及电池热管理领域。解决了传统的电池温度调节技术可分为主动和被动两类。被动散热时通过导热材料、相变材料和散热片等使热量传导和存储，虽然结构简单，但控温能力有限。主动散热包括风冷、液冷和制冷剂冷却等。风冷系统散热效率相对较低，适用于电池功率较小的设备的问题，该电池热管理装置是一种双层热管理架构。本发明通过合理设计双层热管理架构，实现了量子点对电池局部温度的精确监控以及利用电磁感应带动磁流体对电池不同区域的差异化冷却，两层系统通过智能控制器协调工作，避免其相互干扰，极大程度的增强了电池热管理在精准温控以及热量调控效果。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=78e78df7-d44b-4d39-9591-c546be0473f8&amp;shareId=193FC1D0-D471-7F90-B17C-E5CE67738GC2&amp;from=EXPORT&amp;signature=kEqkH37DeThYozUBJyinFYrTEiUZpx1LUXH3yFZeneU%3D&amp;expire=94608000&amp;date=20260626T004136Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=11776872-3db1-45e3-a7ce-1fd48ec7afd6&amp;shareId=52BD9CD7-45FG-8274-0137-9D20G0FC1569&amp;from=EXPORT&amp;signature=3kEVSQrfPlmGj24ygsxuk1XapbqzjpviW7xD2Vi2L6k%3D&amp;expire=94608000&amp;date=20260710T002807Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>包含量子电容器的参数放大器</t>
+          <t>超导量子位中的光控制的二能级系统的量子位选择性调谐</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>微软技术许可有限责任公司</t>
+          <t>国际商业机器公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>萊利 大衛J</t>
+          <t>SANDBERG, MARTIN O. | FALK, ABRAM L. | BALAKRISHNAN, KARTHIK | ORCUTT, JASON S.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -587,17 +587,54 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>描述了与包括量子电容器的参数放大器有关的系统及方法。在一个实例中,提供了包含用于接收量子位元信号的输入端子的参数放大器。参数放大器进一步包括用于接收泵送信号的泵送端子。参数放大器进一步包含放大器,该放大器包括复数个量子电容装置,该复数个量子电容装置经配置以在低温环境中操作,并经配置以借由将量子位元信号与泵送信号混合以产生放大信号来放大量子位元信号。参数放大器进一步包括用于提供放大信号的输出端子。</t>
+          <t>提供了用于减轻量子处理器中的缺陷的影响的方法和系统。减轻系统包括具有多个量子位的量子处理器。该系统包括发光源阵列。每个发光源与量子处理器上的量子位对准。该系统包括控制器,该控制器被配置为接收对量子位的选择并且使得来自发光源阵列的发光源向所选择的量子位发射光。光用于混乱量子处理器中的强耦合的两能级系统(TLS)。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=a933b1a4-1ee7-4584-8654-0684310adaba&amp;shareId=193FC1D0-D471-7F90-B17C-E5CE67738GC2&amp;from=EXPORT&amp;signature=6jWGghLF01f49p61BaiFOq9zGIxcB5bNew4wkAPdLaI%3D&amp;expire=94608000&amp;date=20260626T004136Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=64917608-271c-47fc-88fd-50abd7014bb1&amp;shareId=52BD9CD7-45FG-8274-0137-9D20G0FC1569&amp;from=EXPORT&amp;signature=zuCRJ1pqzhJMVHxQQf6WnpIUmJzQH1H41vBtZYX6Hxs%3D&amp;expire=94608000&amp;date=20260710T002807Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>共集成谐振隧道二极管和高电子迁移率晶体管</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>国际商业机器公司</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CHA, EUNJUNG | ZOTA, BOGDAN CEZAR | MOSELUND, KIRSTEN EMILIE | HNIDA-GUT, KATARZYNA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>本文提供的一种或多种装置和/或方法涉及一种用于制造具有共集成RTD和HEMT的半导体器件的方法。该半导体器件可以包括沿衬底共集成的RTD和HEMT。一种制造方法可以包括:提供包含多个HEMT晶体管层的异质结构;在垂直堆叠结构上形成模板结构,该模板结构包括开口、空腔和种子结构,所述种子结构包括种子材料和种子表面;以及从所述种子表面在模板结构的空腔内生长多个RTD二极管层,其中RTD和HEMT沿衬底共集成。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=d79c53bd-df85-4b34-aaf2-b0d0a448a695&amp;shareId=52BD9CD7-45FG-8274-0137-9D20G0FC1569&amp;from=EXPORT&amp;signature=FiI%2BRLrfMqLhU8XiGlxEeiXKZBNWy%2FNqnCD9LeYiKAk%3D&amp;expire=94608000&amp;date=20260710T002807Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_低温环境系统.xlsx
+++ b/weekly_temp/patents_低温环境系统.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>一种离子阱及量子计算装置</t>
+          <t>一种超流氦中量子涡旋的精确调控装置及方法</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>华翊博奥(北京)量子科技有限公司</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>毛志超 | 蔡明磊 | 梅全鑫 | 赵文定</t>
+          <t>包士然 | 胡应璇 | 黄雯琳 | 骆科旭 | 邱利民</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,34 +476,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本文公开一种离子阱及量子计算装置，包括：一体化基片，制备于一体化基片上的射频电极和直流电极；其中，一体化基片具有轴向的通光开槽。本发明实施例离子阱基于一体化基片设计，消除了温度变化带来的分体错位问题，使得离子阱可以应用于低温环境；通过开放的开槽使离子阱获得了开放式的轴向通光，具有更高的数值孔径，增加了离子阱通光自由度，为实现量子计算的大规模应用提供支持。</t>
+          <t>本发明公开了一种超流氦中量子涡旋的精确调控装置及方法，包括：低温制取与维持系统，包括压缩机、冷水机组、制冷机冷头和液氦室，用于对氦气进行冷却与液化；屏蔽与真空系统，包括真空腔室冷屏、77 K冷屏和4 K冷屏；压力与抽排系统，包括观察室的减压抽空口、减压蝶阀与减压泵组，用于对观察室进行抽排与减压控制；观察与执行单元，包括具有视窗的观察室、布置于观察室内的加热器、由电机驱动的运动格栅、示踪粒子或氦气的注入口以及高速相机；控制系统，与上述各系统电连接并用于协同控制与数据采集。本发明能够在可控低温环境下实现对量子涡旋生成、演化及空间分布进行精确调控与实时观测。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=812af80b-4741-463b-ab78-d83bde6bb6e8&amp;shareId=52BD9CD7-45FG-8274-0137-9D20G0FC1569&amp;from=EXPORT&amp;signature=5LLF1Ckm3n6GVgymHmMHuQotzmM%2BQT%2Bnh9DyXO%2FReCA%3D&amp;expire=94608000&amp;date=20260710T002807Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=328a8ac1-96bf-45f2-a59b-be5d5e70abb3&amp;shareId=CG922F42-3G7E-9G13-CBD4-870541D3C849&amp;from=EXPORT&amp;signature=GJ%2Fb05PLFk38VfcS%2FCaifEAN0%2BnFnFo1DJSf%2Fw3QdLc%3D&amp;expire=94608000&amp;date=20260717T011040Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>一种兼具耐电晕与导热性能的复合纳米芳纶绝缘纸及其制备与应用</t>
+          <t>超导量子芯片的引线键合方法、制造方法和超导量子芯片</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>四川大学</t>
+          <t>深圳量旋科技有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>任俊文 | 张稼珵 | 王梓 | 高萌 | 谭淋 | 陈俊雪 | 龙志慧</t>
+          <t>胡金耀</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,128 +513,54 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本发明公开了一种兼具耐电晕与导热性能的复合纳米芳纶绝缘纸及其制备与应用，绝缘纸由芳纶纳米纤维基体以及均匀分散于芳纶纳米纤维基体中的第一功能填料和第二功能填料组成；第一功能填料为经表面功能化处理的氮化硼量子点；第二功能填料为纳米碳化硅；经表面功能化处理的氮化硼量子点的质量为芳纶纳米纤维基体质量的1%~15%，纳米碳化硅质量为芳纶纳米纤维基体质量的0.5%~8%。经表面功能化处理的氮化硼量子点的平均粒径为2nm~10 nm。本发明解决了现有技术缺乏紫外防护机制，填料分布不可控，工艺复杂导热有限的问题，通过电场调控、紫外防护和复合填料优化分布的协同作用，显著提升绝缘纸的耐电晕性能和导热性能。</t>
+          <t>本申请公开了一种超导量子芯片的引线键合方法、制造方法和超导量子芯片。该方法包括：在印刷电路板的第一金属焊盘上方，利用球焊机激发尖端电流融化焊丝形成第一焊球，并与第一金属焊盘熔融共晶形成第一焊点；在超导量子芯片本体的第二金属焊盘上方，同样形成第二焊球并与第二金属焊盘熔融共晶形成第二焊点；利用劈刀从第二焊点处拉出线弧与第一焊点共晶焊接；最后进行退火处理，以消除引线键合引入的残余应力。本申请通过球焊工艺实现超导量子芯片与印刷电路板之间的熔融共晶键合，并结合退火处理消除残余应力，从而提高了焊点在极低温环境下的连接可靠性和超导量子比特的相干性能。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=3c0b5980-c120-43ac-958a-9b3227662b88&amp;shareId=52BD9CD7-45FG-8274-0137-9D20G0FC1569&amp;from=EXPORT&amp;signature=FycS9fUCKgWV4S3%2Fz0DP0GPwtafHKS%2ByrL9SPMvngXs%3D&amp;expire=94608000&amp;date=20260710T002807Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4d60c6a1-52d1-445e-a53b-2aee07176021&amp;shareId=CG922F42-3G7E-9G13-CBD4-870541D3C849&amp;from=EXPORT&amp;signature=QzR4N6b2g%2BYZ1a6XW4a7rrg01e12bZfPIVfNsf%2B9KbA%3D&amp;expire=94608000&amp;date=20260717T011040Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>一种量子点与电磁感应协同配合的电池热管理装置</t>
+          <t>通过部分侧向开启系统轻松进出</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>安徽理工大学</t>
+          <t>液态空气乔治斯克劳帝方法研究开发股份有限公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>盛国超 | 朱浩冉 | 张妮 | 冯林涛 | 陈晖</t>
+          <t>GAFFET, LUC | GUIA, OLIVIER</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>公开专利</t>
+          <t>授权专利</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本发明提供一种量子点与电磁感应协同配合的电池热管理装置，涉及电池热管理领域。解决了传统的电池温度调节技术可分为主动和被动两类。被动散热时通过导热材料、相变材料和散热片等使热量传导和存储，虽然结构简单，但控温能力有限。主动散热包括风冷、液冷和制冷剂冷却等。风冷系统散热效率相对较低，适用于电池功率较小的设备的问题，该电池热管理装置是一种双层热管理架构。本发明通过合理设计双层热管理架构，实现了量子点对电池局部温度的精确监控以及利用电磁感应带动磁流体对电池不同区域的差异化冷却，两层系统通过智能控制器协调工作，避免其相互干扰，极大程度的增强了电池热管理在精准温控以及热量调控效果。</t>
+          <t>一种制冷系统,包括:由至少第一壁限定的第一低温腔室,该第一低温腔室与至少一个第一冷源热连接;由至少第二壁限定的第二低温腔室,该第二腔室至少部分地面向所述第一壁,该第二腔室包含于所述第一腔室内并与至少一个第二冷源热连接;其中,所述制冷系统包括至少在第一壁上设置的第一门,该第一门与在第二壁上设置的第二门基本相对,所述第一门和所述第二门的设置方式使得当所述第一门打开时,所述第二门也随之打开。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=11776872-3db1-45e3-a7ce-1fd48ec7afd6&amp;shareId=52BD9CD7-45FG-8274-0137-9D20G0FC1569&amp;from=EXPORT&amp;signature=3kEVSQrfPlmGj24ygsxuk1XapbqzjpviW7xD2Vi2L6k%3D&amp;expire=94608000&amp;date=20260710T002807Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>超导量子位中的光控制的二能级系统的量子位选择性调谐</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>国际商业机器公司</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SANDBERG, MARTIN O. | FALK, ABRAM L. | BALAKRISHNAN, KARTHIK | ORCUTT, JASON S.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>提供了用于减轻量子处理器中的缺陷的影响的方法和系统。减轻系统包括具有多个量子位的量子处理器。该系统包括发光源阵列。每个发光源与量子处理器上的量子位对准。该系统包括控制器,该控制器被配置为接收对量子位的选择并且使得来自发光源阵列的发光源向所选择的量子位发射光。光用于混乱量子处理器中的强耦合的两能级系统(TLS)。</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=64917608-271c-47fc-88fd-50abd7014bb1&amp;shareId=52BD9CD7-45FG-8274-0137-9D20G0FC1569&amp;from=EXPORT&amp;signature=zuCRJ1pqzhJMVHxQQf6WnpIUmJzQH1H41vBtZYX6Hxs%3D&amp;expire=94608000&amp;date=20260710T002807Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>共集成谐振隧道二极管和高电子迁移率晶体管</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>国际商业机器公司</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CHA, EUNJUNG | ZOTA, BOGDAN CEZAR | MOSELUND, KIRSTEN EMILIE | HNIDA-GUT, KATARZYNA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>本文提供的一种或多种装置和/或方法涉及一种用于制造具有共集成RTD和HEMT的半导体器件的方法。该半导体器件可以包括沿衬底共集成的RTD和HEMT。一种制造方法可以包括:提供包含多个HEMT晶体管层的异质结构;在垂直堆叠结构上形成模板结构,该模板结构包括开口、空腔和种子结构,所述种子结构包括种子材料和种子表面;以及从所述种子表面在模板结构的空腔内生长多个RTD二极管层,其中RTD和HEMT沿衬底共集成。</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=d79c53bd-df85-4b34-aaf2-b0d0a448a695&amp;shareId=52BD9CD7-45FG-8274-0137-9D20G0FC1569&amp;from=EXPORT&amp;signature=FiI%2BRLrfMqLhU8XiGlxEeiXKZBNWy%2FNqnCD9LeYiKAk%3D&amp;expire=94608000&amp;date=20260710T002807Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=0bbf5322-c2fe-4608-afa5-283fe9534f45&amp;shareId=CG922F42-3G7E-9G13-CBD4-870541D3C849&amp;from=EXPORT&amp;signature=QAfMjsanZO%2F%2FA4mRyKKFu%2BgPvSkkOs5LJvk%2F1%2FwbgjU%3D&amp;expire=94608000&amp;date=20260717T011040Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_低温环境系统.xlsx
+++ b/weekly_temp/patents_低温环境系统.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,54 +456,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>一种超流氦中量子涡旋的精确调控装置及方法</t>
+          <t>包括低温部件的电子设备及其制造方法</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>原子能和替代能源委员会</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>包士然 | 胡应璇 | 黄雯琳 | 骆科旭 | 邱利民</t>
+          <t>THOMAS, CANDICE | CHARBONNIER, JEAN | MICHEL, JEAN-PHILIPPE | GAILLARD, FRÉDÉRIC-XAVIER</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本发明公开了一种超流氦中量子涡旋的精确调控装置及方法，包括：低温制取与维持系统，包括压缩机、冷水机组、制冷机冷头和液氦室，用于对氦气进行冷却与液化；屏蔽与真空系统，包括真空腔室冷屏、77 K冷屏和4 K冷屏；压力与抽排系统，包括观察室的减压抽空口、减压蝶阀与减压泵组，用于对观察室进行抽排与减压控制；观察与执行单元，包括具有视窗的观察室、布置于观察室内的加热器、由电机驱动的运动格栅、示踪粒子或氦气的注入口以及高速相机；控制系统，与上述各系统电连接并用于协同控制与数据采集。本发明能够在可控低温环境下实现对量子涡旋生成、演化及空间分布进行精确调控与实时观测。</t>
+          <t>本发明涉及一种电子设备,包括:- 功能区 (C1),包含配置为在低于 10 K 的温度下工作的低温组件;- 控制区 (C2),包含配置为控制低温组件的电子控制组件;- 被动区 (C3),包含与低温组件和电子控制组件电连接的无源结构 (22),该无源结构 (22) 基于超导材料并集成到介电基体 (13) 中。有利的是,介电基体 (13) 包括围绕无源结构 (22) 的腔体 (52),使得无源结构 (22) 部分悬浮在腔体 (52) 中。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=328a8ac1-96bf-45f2-a59b-be5d5e70abb3&amp;shareId=CG922F42-3G7E-9G13-CBD4-870541D3C849&amp;from=EXPORT&amp;signature=GJ%2Fb05PLFk38VfcS%2FCaifEAN0%2BnFnFo1DJSf%2Fw3QdLc%3D&amp;expire=94608000&amp;date=20260717T011040Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b0138ca7-cf2d-452d-ab90-c573178f8992&amp;shareId=C258CB0C-GCED-81G7-BFGF-3230560BGDD6&amp;from=EXPORT&amp;signature=FW2QRS5fSeeHVnycuVrOQi%2BQwuRMo%2Fyh6xotX4Ff7Kw%3D&amp;expire=94608000&amp;date=20260821T055457Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>超导量子芯片的引线键合方法、制造方法和超导量子芯片</t>
+          <t>一种基于核壳纳米过渡层的石墨膜低温连接方法</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>深圳量旋科技有限公司</t>
+          <t>黑龙江科技大学</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>胡金耀</t>
+          <t>马志鹏 | 庄碧莹 | 杨翟平 | 王伟 | 翟凤龙 | 马庭辉</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,54 +513,91 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本申请公开了一种超导量子芯片的引线键合方法、制造方法和超导量子芯片。该方法包括：在印刷电路板的第一金属焊盘上方，利用球焊机激发尖端电流融化焊丝形成第一焊球，并与第一金属焊盘熔融共晶形成第一焊点；在超导量子芯片本体的第二金属焊盘上方，同样形成第二焊球并与第二金属焊盘熔融共晶形成第二焊点；利用劈刀从第二焊点处拉出线弧与第一焊点共晶焊接；最后进行退火处理，以消除引线键合引入的残余应力。本申请通过球焊工艺实现超导量子芯片与印刷电路板之间的熔融共晶键合，并结合退火处理消除残余应力，从而提高了焊点在极低温环境下的连接可靠性和超导量子比特的相干性能。</t>
+          <t>本发明涉及的是一种基于核壳纳米过渡层的石墨膜低温连接方法，将石墨膜/纳米过渡层/石墨膜的叠层结构温度升至80~350℃，并保持100~120s，实现石墨膜的低温键合，通过低温键合、自适应匹配以及梯度传导的协同效应，实现石墨膜可靠连接；纳米过渡层体系由核壳结构纳米粒子、液晶态分散介质和定向排列助剂制备而成，核壳结构纳米粒子为30~50nm的氮化硼包裹石墨烯量子点构成，液晶态分散介质为含氟苯并环丁烯树脂，定向排列助剂为磁场响应型碳纳米管。本发明提供了具备温度和应力双重响应特性的纳米过渡层体系，并通过低温键合、自适应匹配以及梯度传导的协同效应，成功实现了石墨膜的高效和可靠连接。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=4d60c6a1-52d1-445e-a53b-2aee07176021&amp;shareId=CG922F42-3G7E-9G13-CBD4-870541D3C849&amp;from=EXPORT&amp;signature=QzR4N6b2g%2BYZ1a6XW4a7rrg01e12bZfPIVfNsf%2B9KbA%3D&amp;expire=94608000&amp;date=20260717T011040Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c6fb6182-8541-4808-b3d4-c12b3bb3143c&amp;shareId=C258CB0C-GCED-81G7-BFGF-3230560BGDD6&amp;from=EXPORT&amp;signature=E8SxHt2YXuGgJsRNvRjDY0g80msxDkwodN4PtEZFLxQ%3D&amp;expire=94608000&amp;date=20260821T055457Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>通过部分侧向开启系统轻松进出</t>
+          <t>一种基于钙钛矿微腔双稳态随机共振的弱光时域信号重构方法及装置</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>液态空气乔治斯克劳帝方法研究开发股份有限公司</t>
+          <t>鲁东大学</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GAFFET, LUC | GUIA, OLIVIER</t>
+          <t>韩靖 | 刘燕 | 徐钦峰 | 卢太平 | 朱亚丹 | 李志刚 | 孙兆鹏</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>授权专利</t>
+          <t>公开专利</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>一种制冷系统,包括:由至少第一壁限定的第一低温腔室,该第一低温腔室与至少一个第一冷源热连接;由至少第二壁限定的第二低温腔室,该第二腔室至少部分地面向所述第一壁,该第二腔室包含于所述第一腔室内并与至少一个第二冷源热连接;其中,所述制冷系统包括至少在第一壁上设置的第一门,该第一门与在第二壁上设置的第二门基本相对,所述第一门和所述第二门的设置方式使得当所述第一门打开时,所述第二门也随之打开。</t>
+          <t>本发明涉及非线性光学与光信息处理技术领域，公开了一种基于钙钛矿微腔双稳态随机共振的弱光时域信号重构方法及装置。所述方法利用包含钙钛矿材料的光学微腔在低温连续波激发条件下产生的双稳态响应，调节微腔工作温度及腔长，使系统工作于双稳态临界区域；通过向承载弱光时域信号的输入光场中引入可控噪声，利用噪声诱导的随机共振效应，提高弱光时域信号触发双稳态状态跃迁的概率，从而实现微弱信号的重构。本发明构建了一种基于钙钛矿微腔双稳态的光学随机共振平台，具有驱动功率低、灵敏度高、参数可调、易于集成等优点，可应用于量子探测、片上光信息处理及全光信号再生等领域。同时，本发明还可利用钙钛矿微腔偏振双稳态特性实现偏振态恢复功能。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=0bbf5322-c2fe-4608-afa5-283fe9534f45&amp;shareId=CG922F42-3G7E-9G13-CBD4-870541D3C849&amp;from=EXPORT&amp;signature=QAfMjsanZO%2F%2FA4mRyKKFu%2BgPvSkkOs5LJvk%2F1%2FwbgjU%3D&amp;expire=94608000&amp;date=20260717T011040Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=43d07039-dc66-4b45-81a5-27b28b756918&amp;shareId=C258CB0C-GCED-81G7-BFGF-3230560BGDD6&amp;from=EXPORT&amp;signature=Y0cbK%2FtjY3tk2d11qWyl5itHf7Z9MQXjBDcYFcroxH4%3D&amp;expire=94608000&amp;date=20260821T055457Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>量子计算机、电子设备和传输线系统</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>本发明提供了一种量子计算机,其在低温下运行时可减少从传输路径流入的热量。该量子计算机采用低热传输光纤。该量子计算机包括第一光纤、第二光纤、将电信号转换为光信号的电/光转换器、将光信号转换为电信号的光电转换器以及量子运算模块。通过第一光纤传输的光信号由光电转换器转换为电信号,量子运算模块接收转换后的电信号,量子运算模块对接收到的电信号进行运算,量子运算模块发送计算后的电信号,发送的电信号由光电转换器转换为光信号,转换后的光信号通过第二光纤传输。第一光纤、第二光纤和量子运算模块均布置在低温区域。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=aabb57ea-f0ca-4de9-b552-e4ce25fda8df&amp;shareId=C258CB0C-GCED-81G7-BFGF-3230560BGDD6&amp;from=EXPORT&amp;signature=4wl3qOB7pGeIgpSgw15tkal5GO%2BZIVVdzK0p95%2BV8Ds%3D&amp;expire=94608000&amp;date=20260821T055457Z&amp;version=1.0</t>
         </is>
       </c>
     </row>

--- a/weekly_temp/patents_低温环境系统.xlsx
+++ b/weekly_temp/patents_低温环境系统.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>包括低温部件的电子设备及其制造方法</t>
+          <t>利用超导刚挠性电路在量子比特表面和量子比特表面控制系统之间维持高热梯度的系统和方法。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>原子能和替代能源委员会</t>
+          <t>微软技术许可有限责任公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>THOMAS, CANDICE | CHARBONNIER, JEAN | MICHEL, JEAN-PHILIPPE | GAILLARD, FRÉDÉRIC-XAVIER</t>
+          <t>ターナー,マシュー デイビッド | ランタ,クレイグ スティーブン | クレイマー,ケビン ジェームス</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,34 +476,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本发明涉及一种电子设备,包括:- 功能区 (C1),包含配置为在低于 10 K 的温度下工作的低温组件;- 控制区 (C2),包含配置为控制低温组件的电子控制组件;- 被动区 (C3),包含与低温组件和电子控制组件电连接的无源结构 (22),该无源结构 (22) 基于超导材料并集成到介电基体 (13) 中。有利的是,介电基体 (13) 包括围绕无源结构 (22) 的腔体 (52),使得无源结构 (22) 部分悬浮在腔体 (52) 中。</t>
+          <t>本文描述了一种用于在量子比特表面和量子比特表面控制系统之间维持高热梯度的系统和方法。该系统包括与超导刚挠性电路的第一刚性电路部分关联的量子比特表面,以及与该超导刚挠性电路的第二刚性电路部分关联的控制系统。该超导刚挠性电路包括用于连接第一刚性电路部分和第二刚性电路部分的柔性电路部分。该系统还包括第一冷却系统,其能够将量子比特表面和超导刚挠性电路的第一刚性电路部分的工作温度维持在100毫开尔文以下。该系统还包括控制系统和第二冷却系统,其能够将超导刚挠性电路的第二刚性电路部分的工作温度维持在10开尔文以下。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=b0138ca7-cf2d-452d-ab90-c573178f8992&amp;shareId=C258CB0C-GCED-81G7-BFGF-3230560BGDD6&amp;from=EXPORT&amp;signature=FW2QRS5fSeeHVnycuVrOQi%2BQwuRMo%2Fyh6xotX4Ff7Kw%3D&amp;expire=94608000&amp;date=20260821T055457Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=f09696bb-8816-4864-a2c1-3f0831f74505&amp;shareId=F0B99893-G204-5B3D-209G-6B3G48021D31&amp;from=EXPORT&amp;signature=0exuMOqA5gaxVMS487H2VnybrcRxjsaiNFRkCZV520Y%3D&amp;expire=94608000&amp;date=20260828T063441Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>一种基于核壳纳米过渡层的石墨膜低温连接方法</t>
+          <t>一种具有宽温域压卡效应的复合量子点温度记忆材料及其制备方法和应用</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>黑龙江科技大学</t>
+          <t>二四九五企业管理(珠海)有限公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>马志鹏 | 庄碧莹 | 杨翟平 | 王伟 | 翟凤龙 | 马庭辉</t>
+          <t>梁海 | 胡艳梅</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,34 +513,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本发明涉及的是一种基于核壳纳米过渡层的石墨膜低温连接方法，将石墨膜/纳米过渡层/石墨膜的叠层结构温度升至80~350℃，并保持100~120s，实现石墨膜的低温键合，通过低温键合、自适应匹配以及梯度传导的协同效应，实现石墨膜可靠连接；纳米过渡层体系由核壳结构纳米粒子、液晶态分散介质和定向排列助剂制备而成，核壳结构纳米粒子为30~50nm的氮化硼包裹石墨烯量子点构成，液晶态分散介质为含氟苯并环丁烯树脂，定向排列助剂为磁场响应型碳纳米管。本发明提供了具备温度和应力双重响应特性的纳米过渡层体系，并通过低温键合、自适应匹配以及梯度传导的协同效应，成功实现了石墨膜的高效和可靠连接。</t>
+          <t>本发明公开了一种具有宽温域压卡效应的复合量子点温度记忆材料及其制备方法和应用，属于温控材料技术领域。该复合量子点温度记忆材料为碳量子点/压卡塑晶材料复合物，其具有能在温度变化时发生可逆性畸变的晶格结构，所述可逆性畸变为：当温度升高时，晶格扩张，吸收外界热量；当温度降低时，晶格收缩，释放储存的热量。该材料通过吸放热循环，并依托压卡效应实现‑80℃~300℃全温区精准温度记忆，温区覆盖范围广，在极端温度下无脆裂、无分解、无性能衰减，压卡效应稳定，温度记忆误差不超过±1℃，能适配于多种不同成型方式，能很好地满足建筑陶瓷、制冷板材、建筑墙面、工业设备、汽车表面、温控零部件等不同应用场景的使用需求。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=c6fb6182-8541-4808-b3d4-c12b3bb3143c&amp;shareId=C258CB0C-GCED-81G7-BFGF-3230560BGDD6&amp;from=EXPORT&amp;signature=E8SxHt2YXuGgJsRNvRjDY0g80msxDkwodN4PtEZFLxQ%3D&amp;expire=94608000&amp;date=20260821T055457Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=dc3036ca-3eac-4d77-8d83-851d81bd4963&amp;shareId=F0B99893-G204-5B3D-209G-6B3G48021D31&amp;from=EXPORT&amp;signature=NtmkojEFFHucszTPYOjn5Xk1rrF0gAgJuKJJt2AGmwk%3D&amp;expire=94608000&amp;date=20260828T063441Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>一种基于钙钛矿微腔双稳态随机共振的弱光时域信号重构方法及装置</t>
+          <t>全封闭式微流压力控制系统及方法</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>鲁东大学</t>
+          <t>中国科学院理化技术研究所 | 北京石油化工学院</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>韩靖 | 刘燕 | 徐钦峰 | 卢太平 | 朱亚丹 | 李志刚 | 孙兆鹏</t>
+          <t>高波 | 韩东旭 | 宇波 | 王齐 | 孙东亮 | 张海洋 | 孔祥杰</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -550,34 +550,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本发明涉及非线性光学与光信息处理技术领域，公开了一种基于钙钛矿微腔双稳态随机共振的弱光时域信号重构方法及装置。所述方法利用包含钙钛矿材料的光学微腔在低温连续波激发条件下产生的双稳态响应，调节微腔工作温度及腔长，使系统工作于双稳态临界区域；通过向承载弱光时域信号的输入光场中引入可控噪声，利用噪声诱导的随机共振效应，提高弱光时域信号触发双稳态状态跃迁的概率，从而实现微弱信号的重构。本发明构建了一种基于钙钛矿微腔双稳态的光学随机共振平台，具有驱动功率低、灵敏度高、参数可调、易于集成等优点，可应用于量子探测、片上光信息处理及全光信号再生等领域。同时，本发明还可利用钙钛矿微腔偏振双稳态特性实现偏振态恢复功能。</t>
+          <t>本发明提供一种全封闭式微流压力控制系统及方法，涉及深低温计量与精密压力控制技术领域，该系统包括第一低温恒温器和第二低温恒温器；连通管路，连接两个恒温器的气相空间，构成全封闭气体回路；气体流量控制阀门，设置于连通管路上；主动控温单元，与第二低温恒温器热耦合；中央控制系统，用于根据第一低温恒温器的实际压力与目标压力的偏差，控制主动控温单元调节第二低温恒温器的温度以产生压差，并根据偏差控制气体流量控制阀门的开度，使工作气体在全封闭气体回路中转移，以调节第一低温恒温器的内部压力。本发明实现了工作气体的零损耗循环利用，适用于极低温物理实验、量子计算及低温恒温器等应用场景中的高精度压力控制。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=43d07039-dc66-4b45-81a5-27b28b756918&amp;shareId=C258CB0C-GCED-81G7-BFGF-3230560BGDD6&amp;from=EXPORT&amp;signature=Y0cbK%2FtjY3tk2d11qWyl5itHf7Z9MQXjBDcYFcroxH4%3D&amp;expire=94608000&amp;date=20260821T055457Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=07e972eb-1196-40f9-b6f1-bfcd0f5905b6&amp;shareId=F0B99893-G204-5B3D-209G-6B3G48021D31&amp;from=EXPORT&amp;signature=ZfXNz42H5rbaimAtbqpNRKox0%2B2%2FA7MrsdsKpS6%2BbQw%3D&amp;expire=94608000&amp;date=20260828T063441Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>量子计算机、电子设备和传输线系统</t>
+          <t>分布式热管理架构</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>高通股份有限公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ルイ、ルイ | アルトン、ロナルド | ウィリアム、スマリン | メへトレ、ビナヤック·ナナ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -587,17 +587,54 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>本发明提供了一种量子计算机,其在低温下运行时可减少从传输路径流入的热量。该量子计算机采用低热传输光纤。该量子计算机包括第一光纤、第二光纤、将电信号转换为光信号的电/光转换器、将光信号转换为电信号的光电转换器以及量子运算模块。通过第一光纤传输的光信号由光电转换器转换为电信号,量子运算模块接收转换后的电信号,量子运算模块对接收到的电信号进行运算,量子运算模块发送计算后的电信号,发送的电信号由光电转换器转换为光信号,转换后的光信号通过第二光纤传输。第一光纤、第二光纤和量子运算模块均布置在低温区域。</t>
+          <t>该热管理配置包括串行数据总线、中央处理器 (CPU)、图形处理器 (GPU)、神经信号处理器 (NSP) 和始终开启子系统 (AOSS),所述串行数据总线、CPU、GPU、NSP 和 AOSS 均在片上系统 (SoC) 上实现,所述 CPU 包括第一组热传感器和第一组控制器,所述第一组热传感器分别与所述第一组控制器耦合,所述 NSP 包括第二组热传感器和第二组控制器,所述第二组热传感器分别与所述第二组控制器耦合,所述 AOSS 包括第三组热传感器和第三组控制器,所述第三组热传感器分别与所述第三组控制器耦合。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=aabb57ea-f0ca-4de9-b552-e4ce25fda8df&amp;shareId=C258CB0C-GCED-81G7-BFGF-3230560BGDD6&amp;from=EXPORT&amp;signature=4wl3qOB7pGeIgpSgw15tkal5GO%2BZIVVdzK0p95%2BV8Ds%3D&amp;expire=94608000&amp;date=20260821T055457Z&amp;version=1.0</t>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=9e525ecd-ec72-457f-87bd-e62d957e01dd&amp;shareId=F0B99893-G204-5B3D-209G-6B3G48021D31&amp;from=EXPORT&amp;signature=aSfBPlQNyidymusHNeE6bS1zW4%2FxWbFhLk4UMzjPgbg%3D&amp;expire=94608000&amp;date=20260828T063441Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>处理器组装、量子计算设备和方法</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IQM芬兰公司</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>사이라 올리-펜티 | 오르지아치 장-룩 | 라틴마키 파시</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>一种用于量子计算机的处理器组件包括载体、安装在载体上的至少一个量子处理器芯片以及与载体热接触的第一热锚点。该组件还包括第一电连接器和电信号连接,该电信号连接的第一端与载体电连接,第二端与第一电连接器电连接。该处理器组件还包括第二热锚点。第二热锚点与第一热锚点热隔离,并且第二热锚点与第一电连接器热接触。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=afa45580-d889-434e-8bc4-b28f285c8eba&amp;shareId=F0B99893-G204-5B3D-209G-6B3G48021D31&amp;from=EXPORT&amp;signature=jVudAUQGTXmDcdJjsHp%2FNIGKdD7l8OkY1cbULi6SSAY%3D&amp;expire=94608000&amp;date=20260828T063441Z&amp;version=1.0</t>
         </is>
       </c>
     </row>
